--- a/ri_plus_4438/urdf/initial_joint_properties.xlsx
+++ b/ri_plus_4438/urdf/initial_joint_properties.xlsx
@@ -1405,34 +1405,34 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.07421078</v>
+        <v>0.06406078</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.01603516</v>
+        <v>0.01860227</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.05927323</v>
+        <v>0.05889209</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-0.00696726</v>
+        <v>-0.00134131</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.095e-05</v>
+        <v>1.275e-05</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>3.52e-06</v>
+        <v>3.03e-06</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-9.459999999999999e-06</v>
+        <v>-1.64e-06</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>4.907e-05</v>
+        <v>2.778e-05</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>1.11e-06</v>
+        <v>1.4e-07</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>3.063e-05</v>
+        <v>2.573e-05</v>
       </c>
     </row>
     <row r="27">
@@ -1442,34 +1442,34 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.07421078</v>
+        <v>0.06406078</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.01603516</v>
+        <v>0.01860227</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.05927323</v>
+        <v>-0.05889209</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.00465155</v>
+        <v>0.00134131</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.295e-05</v>
+        <v>1.275e-05</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.52e-06</v>
+        <v>-3.03e-06</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-6.62e-06</v>
+        <v>1.64e-06</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>5.106e-05</v>
+        <v>2.778e-05</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-9e-07</v>
+        <v>1.4e-07</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>3.063e-05</v>
+        <v>2.573e-05</v>
       </c>
     </row>
   </sheetData>
